--- a/TestCase/TV.xlsx
+++ b/TestCase/TV.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\NGA Training\Assignment SDET\Day 14\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\SDET_Wipro\TestCase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1625983D-ED64-46A8-BFE7-2004B0D908A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB70CFD-B4D3-4637-82D5-CC4AC8AB4B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4D67B6FC-63A5-4664-9C45-46C78102EF37}"/>
+    <workbookView xWindow="3675" yWindow="2925" windowWidth="15375" windowHeight="7875" xr2:uid="{4D67B6FC-63A5-4664-9C45-46C78102EF37}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="108">
   <si>
     <t>SR. NO.</t>
   </si>
@@ -349,6 +349,21 @@
   </si>
   <si>
     <t>TV downloads and installs updates successfully</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Pixcel Clarity</t>
+  </si>
+  <si>
+    <t>Audio and Videp Sync</t>
+  </si>
+  <si>
+    <t>TV Physical Btn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TV cable </t>
   </si>
 </sst>
 </file>
@@ -738,7 +753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C0A23B3-123D-46A5-A40A-79C5B10628A5}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1141,6 +1156,31 @@
         <v>102</v>
       </c>
     </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C17" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C18" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C19" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C20" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C21" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
